--- a/base_datas/media_nacional_detalhamento.xlsx
+++ b/base_datas/media_nacional_detalhamento.xlsx
@@ -587,148 +587,148 @@
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>populacao_24</t>
+          <t>populacao_25</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>657.906128935444</v>
+        <v>785.0161963624008</v>
       </c>
       <c r="B2">
-        <v>173.8196139099241</v>
+        <v>180.9512246234176</v>
       </c>
       <c r="C2">
-        <v>6832.743459847115</v>
+        <v>7535.596714562197</v>
       </c>
       <c r="D2">
-        <v>389.7008261691104</v>
+        <v>459.0692486007583</v>
       </c>
       <c r="E2">
-        <v>601.9841628377819</v>
+        <v>721.4671589670048</v>
       </c>
       <c r="F2">
-        <v>54.20861562466339</v>
+        <v>61.34664108726943</v>
       </c>
       <c r="G2">
-        <v>16.50236859554457</v>
+        <v>18.13456026894213</v>
       </c>
       <c r="H2">
-        <v>240.2296292986271</v>
+        <v>256.6162582674043</v>
       </c>
       <c r="I2">
-        <v>66.67048953546843</v>
+        <v>70.34547167474553</v>
       </c>
       <c r="J2">
-        <v>12.66563767793719</v>
+        <v>2.318740029603504</v>
       </c>
       <c r="K2">
-        <v>4068.926955982995</v>
+        <v>4537.619404882741</v>
       </c>
       <c r="L2">
-        <v>1779.353406748903</v>
+        <v>1938.842607909603</v>
       </c>
       <c r="M2">
-        <v>986.2508451516062</v>
+        <v>1060.270717482691</v>
       </c>
       <c r="N2">
-        <v>237.5044061729009</v>
+        <v>322.5149649947491</v>
       </c>
       <c r="O2">
-        <v>128.0527979006407</v>
+        <v>110.8446652461726</v>
       </c>
       <c r="P2">
-        <v>8.765542271102587</v>
+        <v>10.62665377292406</v>
       </c>
       <c r="Q2">
-        <v>10.61667910088558</v>
+        <v>10.78904654154204</v>
       </c>
       <c r="R2">
-        <v>76.32910555035717</v>
+        <v>73.55191672171813</v>
       </c>
       <c r="S2">
-        <v>78.11405439717291</v>
+        <v>125.7777394042518</v>
       </c>
       <c r="T2">
-        <v>82.62388821800103</v>
+        <v>91.26054366302479</v>
       </c>
       <c r="U2">
-        <v>251.6656890497605</v>
+        <v>280.6616842066475</v>
       </c>
       <c r="V2">
-        <v>190.2196539031093</v>
+        <v>224.379248879704</v>
       </c>
       <c r="W2">
-        <v>3928.699041553994</v>
+        <v>4203.961932344067</v>
       </c>
       <c r="X2">
-        <v>619.6702869300105</v>
+        <v>660.8749918098674</v>
       </c>
       <c r="Y2">
-        <v>5.315492108569766</v>
+        <v>5.424277189996325</v>
       </c>
       <c r="Z2">
-        <v>24.73324089545927</v>
+        <v>27.87990517766868</v>
       </c>
       <c r="AA2">
-        <v>36.13219371644946</v>
+        <v>40.35091026121903</v>
       </c>
       <c r="AB2">
-        <v>2.845496509466277E-16</v>
+        <v>1.008543988488698E-16</v>
       </c>
       <c r="AC2">
-        <v>9.39919425056576</v>
+        <v>12.73007207110482</v>
       </c>
       <c r="AD2">
-        <v>12.86130598797305</v>
+        <v>10.39237772493542</v>
       </c>
       <c r="AE2">
-        <v>35.54273628572435</v>
+        <v>33.8248801955621</v>
       </c>
       <c r="AF2">
-        <v>7.277793482567173</v>
+        <v>9.806215829025755</v>
       </c>
       <c r="AG2">
-        <v>2717.390378325714</v>
+        <v>3022.811993947558</v>
       </c>
       <c r="AH2">
-        <v>429.4473048975834</v>
+        <v>467.5037520550409</v>
       </c>
       <c r="AI2">
-        <v>193.2533378638279</v>
+        <v>198.2630925975667</v>
       </c>
       <c r="AJ2">
-        <v>588.8558996320795</v>
+        <v>670.4519011151408</v>
       </c>
       <c r="AK2">
-        <v>120.9052166859761</v>
+        <v>120.0970056452453</v>
       </c>
       <c r="AL2">
-        <v>407.8467957606125</v>
+        <v>390.6600442146365</v>
       </c>
       <c r="AM2">
-        <v>40.79999927054286</v>
+        <v>40.53887823915556</v>
       </c>
       <c r="AN2">
-        <v>159.8449036961663</v>
+        <v>141.0548202417746</v>
       </c>
       <c r="AO2">
-        <v>1377.955076962981</v>
+        <v>1484.931588553425</v>
       </c>
       <c r="AP2">
-        <v>144.2395690427456</v>
+        <v>155.4892148845773</v>
       </c>
       <c r="AQ2">
-        <v>110.1226931333414</v>
+        <v>129.6698493162134</v>
       </c>
       <c r="AR2">
-        <v>13.20452041699421</v>
+        <v>20.24652714581114</v>
       </c>
       <c r="AS2">
-        <v>36.29005091324641</v>
+        <v>43.97749600459942</v>
       </c>
       <c r="AT2">
-        <v>158.0198538746868</v>
+        <v>165.8125893357729</v>
       </c>
       <c r="AU2">
         <v>1</v>
